--- a/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -503,7 +503,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -595,7 +595,7 @@
     <t>Bundle.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>

--- a/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}ch-elm-leading-code:The ServiceRequest.code and the Observation.code are in general equal. {entry.resource.ofType(ServiceRequest).code = entry.resource.ofType(Observation).code}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}ch-elm-leading-code:The ServiceRequest.code and the Observation.code are in general equal. {entry.resource.ofType(ServiceRequest).code = entry.resource.ofType(Observation).code}ch-elm-patient-birthdate:If a Patient entry has a birthDate set, it must be &gt;= 1900-01-01 and before the Bundle's creation date (timestamp). {entry.resource.ofType(Patient).where(birthDate.exists() and birthDate.hasValue()).all(birthDate &gt;= @1900-01-01 and ((birthDate.toString().length()=4 and birthDate &lt;= %resource.timestamp.toString().substring(0,4).toDateTime()) or (birthDate.toString().length()=7 and birthDate &lt;= %resource.timestamp.toString().substring(0,7).toDateTime()) or (birthDate.toString().length()=10 and birthDate &lt;= %resource.timestamp.toString().substring(0,10).toDateTime())))}</t>
   </si>
   <si>
     <t>N/A</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-document-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
